--- a/output/pdf_financials_xlsx/PLNK.xlsx
+++ b/output/pdf_financials_xlsx/PLNK.xlsx
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>6.543083</v>
+        <v>6.753035</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>6.543083</v>
+        <v>6.807731</v>
       </c>
     </row>
     <row r="93">
@@ -2804,7 +2804,11 @@
           <t>Share based payment reserves 12</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.209952</v>
       </c>
@@ -4754,7 +4758,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0.296705</v>
+        <v>-0.296705</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>-0.045023</v>

--- a/output/pdf_financials_xlsx/PLNK.xlsx
+++ b/output/pdf_financials_xlsx/PLNK.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.051303</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.120094</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.852392</v>
+        <v>0.903695</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.316256</v>
+        <v>-1.196162</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.852392</v>
+        <v>0.903695</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.316256</v>
+        <v>-1.196162</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>15.83432283299574</v>
+        <v>16.78734475753419</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-25.33209186601545</v>
+        <v>-23.02081484957088</v>
       </c>
     </row>
     <row r="31">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.012603</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.012603</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -3614,7 +3614,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>-0.012603</v>
       </c>
@@ -4102,7 +4106,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
@@ -4130,7 +4134,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
@@ -4862,7 +4866,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">

--- a/output/pdf_financials_xlsx/PLNK.xlsx
+++ b/output/pdf_financials_xlsx/PLNK.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.852392</v>
+        <v>0.85861</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-1.316256</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.006218</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.903695</v>
+        <v>0.909913</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.196162</v>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.903695</v>
+        <v>0.909913</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.196162</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>16.78734475753419</v>
+        <v>16.90285243402056</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-23.02081484957088</v>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>0.7241937550226529</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.191828</v>
       </c>
     </row>
     <row r="65">
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>2.190147</v>
       </c>
     </row>
     <row r="68">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004922</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003062</v>
       </c>
     </row>
     <row r="112">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004922</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003062</v>
       </c>
     </row>
     <row r="135">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.13091</v>
+        <v>-0.135832</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>0.12956</v>
+        <v>0.126498</v>
       </c>
     </row>
   </sheetData>
@@ -3148,7 +3148,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>-0.006218</v>
       </c>
@@ -3464,7 +3468,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>-0.004922</v>
       </c>
@@ -4314,7 +4322,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>0.006218</v>
       </c>
